--- a/feedback_forms/026_donor_story_submission_request_form--feedback_forms.xlsx
+++ b/feedback_forms/026_donor_story_submission_request_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Submission Form Options</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Additional Info Options</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Assigned Form Label</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -868,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1207,46 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>additional_info_options_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>additional_info_options_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option_5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Option 5</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
